--- a/READING/4_21_12.xlsx
+++ b/READING/4_21_12.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -504,33 +504,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>あらためて</t>
+          <t>取り入れる</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>重新，再次</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>引进，采纳</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>とりいれる</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>〜にびっくりする</t>
+          <t>〜にもとづいて</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>对...感到惊讶</t>
+          <t>根据...，基于...</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -538,75 +542,71 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>〜にしろ〜にしろ</t>
+          <t>いままで</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>无论是...还是...</t>
+          <t>到现在为止</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>これまで-&gt;过往，以前</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ずいぶん</t>
+          <t>あたりまえに</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>相当，非常</t>
+          <t>理所当然地</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ぷつんと-&gt;急匆匆地</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>助手席</t>
+          <t>こいつら</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>副驾驶座</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>じょしゅせき</t>
-        </is>
-      </c>
+          <t>这些家伙们（粗鲁说法）</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ぽつんと</t>
+          <t>かえって</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>孤零零地</t>
+          <t>反而，反倒</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -614,16 +614,16 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>いずれも</t>
+          <t>いざ〜となると</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>任意的</t>
+          <t>一旦到了...的时候</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>わずか</t>
+          <t>なりきる</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>仅仅，一点点</t>
+          <t>完全变成，扮演得惟妙惟肖</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -648,16 +648,16 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>～ように</t>
+          <t>〜とする</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>正如…;为了…</t>
+          <t>视为...，当作...</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -665,16 +665,16 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>あらゆる</t>
+          <t>〜にしたがって</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>所有的，一切的</t>
+          <t>随着...；遵照...</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -682,100 +682,96 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>〜方がいる</t>
+          <t>〜がないか</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>有...的人（敬语）</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>〜かたがいる</t>
-        </is>
-      </c>
+          <t>是否…</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>される方</t>
+          <t>求める</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>被动表尊他</t>
+          <t>购买,寻求，要求</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>されるかた</t>
+          <t>もとめる</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>迷惑になります</t>
+          <t>〜の場合</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>会给人添麻烦</t>
+          <t>...的情况下</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>めいわくになります</t>
+          <t>〜のばあい</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>受験する</t>
+          <t>改めて</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>参加考试</t>
+          <t>重新，再次</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>じゅけんする</t>
+          <t>あらためて</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>しっかり</t>
+          <t>だって</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>踏实地,好好地，牢固地</t>
+          <t>因为；即便是</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -783,21 +779,21 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>〜に通う</t>
+          <t>受け持つ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>定期去（某地）</t>
+          <t>负责，担任</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>〜にかよう</t>
+          <t>うけもつ</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -808,12 +804,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>つい</t>
+          <t>ようです</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>不由得，不知不觉地</t>
+          <t>好像...，似乎...</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -821,33 +817,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>〜とする</t>
+          <t>〜と暗示している</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>视为...，当作...</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>暗示着...</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>〜とあんじしている</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>〜につながる</t>
+          <t>あらためて</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>与...相连，导致...</t>
+          <t>重新，再次</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -855,33 +855,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>すでに</t>
+          <t>〜方がいる</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>已经</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>有...的人（敬语）</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>〜かたがいる</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ようです</t>
+          <t>ぽつんと</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>好像...，似乎...</t>
+          <t>孤零零地</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -889,37 +893,33 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>取り入れる</t>
+          <t>〜にびっくりする</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>引进，采纳</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>とりいれる</t>
-        </is>
-      </c>
+          <t>对...感到惊讶</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>〜にもとづいて</t>
+          <t>わずか</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>根据...，基于...</t>
+          <t>仅仅，一点点</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -927,37 +927,33 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>いままで</t>
+          <t>いずれも</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>到现在为止</t>
+          <t>任意的</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>これまで-&gt;过往，以前</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>あたりまえに</t>
+          <t>つい</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>理所当然地</t>
+          <t>不由得，不知不觉地</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -965,16 +961,16 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>こいつら</t>
+          <t>しっかり</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>这些家伙们（粗鲁说法）</t>
+          <t>踏实地,好好地，牢固地</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -982,16 +978,16 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>かえって</t>
+          <t>はずかしい</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>反而，反倒</t>
+          <t>害羞的，不好意思的</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -999,16 +995,16 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>いざ〜となると</t>
+          <t>〜にしろ〜にしろ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>一旦到了...的时候</t>
+          <t>无论是...还是...</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1016,58 +1012,66 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>〜と暗示している</t>
+          <t>助手席</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>暗示着...</t>
+          <t>副驾驶座</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>〜とあんじしている</t>
+          <t>じょしゅせき</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>におい</t>
+          <t>ずいぶん</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>味道，气味</t>
+          <t>相当，非常</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ぷつんと-&gt;急匆匆地</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>なりきる</t>
+          <t>〜となっている</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>完全变成，扮演得惟妙惟肖</t>
+          <t>(规定、状态)是...</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>～ことになります-&gt;规定…</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1075,12 +1079,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>〜のは〜ためだ・からだ</t>
+          <t>これまで</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>(之所以)...是因为...</t>
+          <t>至今为止</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1092,33 +1096,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>働き</t>
+          <t>なお</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>工作；作用</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>はたらき</t>
-        </is>
-      </c>
+          <t>另外，再者</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>〜を〜する</t>
+          <t>まるで〜ように</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>担任(职务)，使(状态)</t>
+          <t>简直就像...一样</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1126,16 +1126,16 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>もともと</t>
+          <t>～っていうのは</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>原本，本来</t>
+          <t>所谓…</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1147,19 +1147,15 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>お願いがあります</t>
+          <t>どうせ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>有事相求</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>おねがいがあります</t>
-        </is>
-      </c>
+          <t>反正，总归</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
@@ -1168,36 +1164,36 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>サークル</t>
+          <t>用件</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>社团，圈子</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>事情，要事</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ようけん</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>持参</t>
+          <t>まとめ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>带来，自备</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>じさん</t>
-        </is>
-      </c>
+          <t>总结，归纳</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -1206,12 +1202,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>そのため</t>
+          <t>～によって</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>因此，所以</t>
+          <t>通过…</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1223,29 +1219,33 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>〜できませんでしょうか</t>
+          <t>作り声</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>能否...呢？（礼貌请求）</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>假声</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>つくりごえ</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>〜にしたがって</t>
+          <t>〜につながる</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>随着...；遵照...</t>
+          <t>与...相连，导致...</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1257,33 +1257,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>用件</t>
+          <t>そのため</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>事情，要事</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>ようけん</t>
-        </is>
-      </c>
+          <t>因此，所以</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>〜がないか</t>
+          <t>〜できませんでしょうか</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>是否…</t>
+          <t>能否...呢？（礼貌请求）</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1291,42 +1287,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>求める</t>
+          <t>におい</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>购买,寻求，要求</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>もとめる</t>
-        </is>
-      </c>
+          <t>味道，气味</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>〜の場合</t>
+          <t>〜に通う</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>...的情况下</t>
+          <t>定期去（某地）</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>〜のばあい</t>
+          <t>〜にかよう</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -1337,20 +1329,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>〜となっている</t>
+          <t>受験する</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>(规定、状态)是...</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>～ことになります-&gt;规定…</t>
-        </is>
-      </c>
+          <t>参加考试</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>じゅけんする</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1358,15 +1350,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>これまで</t>
+          <t>迷惑になります</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>至今为止</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>会给人添麻烦</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>めいわくになります</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
@@ -1375,50 +1371,50 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>なお</t>
+          <t>される方</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>另外，再者</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>被动表尊他</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>されるかた</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>改めて</t>
+          <t>あらゆる</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>重新，再次</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>あらためて</t>
-        </is>
-      </c>
+          <t>所有的，一切的</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>だって</t>
+          <t>～ように</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>因为；即便是</t>
+          <t>正如…;为了…</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -1430,12 +1426,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>どうせ</t>
+          <t>〜のは〜ためだ・からだ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>反正，总归</t>
+          <t>(之所以)...是因为...</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -1443,23 +1439,19 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>受け持つ</t>
+          <t>すでに</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>负责，担任</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>うけもつ</t>
-        </is>
-      </c>
+          <t>已经</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -1468,15 +1460,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>まとめ</t>
+          <t>働き</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>总结，归纳</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>工作；作用</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>はたらき</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -1485,12 +1481,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>～によって</t>
+          <t>〜を〜する</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>通过…</t>
+          <t>担任(职务)，使(状态)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -1502,12 +1498,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>～っていうのは</t>
+          <t>もともと</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>所谓…</t>
+          <t>原本，本来</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -1519,15 +1515,19 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>はずかしい</t>
+          <t>お願いがあります</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>害羞的，不好意思的</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>有事相求</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>おねがいがあります</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
@@ -1536,19 +1536,15 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>作り声</t>
+          <t>サークル</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>假声</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>つくりごえ</t>
-        </is>
-      </c>
+          <t>社团，圈子</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -1557,15 +1553,19 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>まるで〜ように</t>
+          <t>持参</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>简直就像...一样</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>带来，自备</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>じさん</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">

--- a/READING/4_21_12.xlsx
+++ b/READING/4_21_12.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -487,40 +487,40 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>あろう</t>
+          <t>求める</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>同“だろう”</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>购买,寻求，要求</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>もとめる</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>取り入れる</t>
+          <t>しっかり</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>引进，采纳</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>とりいれる</t>
-        </is>
-      </c>
+          <t>踏实地,好好地，牢固地</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -529,12 +529,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>〜にもとづいて</t>
+          <t>つい</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>根据...，基于...</t>
+          <t>不由得，不知不觉地</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -542,24 +542,20 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>いままで</t>
+          <t>いずれも</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>到现在为止</t>
+          <t>任意的</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>これまで-&gt;过往，以前</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -567,12 +563,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>あたりまえに</t>
+          <t>わずか</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>理所当然地</t>
+          <t>仅仅，一点点</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -580,16 +576,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>こいつら</t>
+          <t>ぽつんと</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>这些家伙们（粗鲁说法）</t>
+          <t>孤零零地</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -601,29 +597,33 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>かえって</t>
+          <t>〜方がいる</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>反而，反倒</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>有...的人（敬语）</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>〜かたがいる</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>いざ〜となると</t>
+          <t>あらためて</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>一旦到了...的时候</t>
+          <t>重新，再次</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -631,50 +631,58 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>なりきる</t>
+          <t>〜と暗示している</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>完全变成，扮演得惟妙惟肖</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>暗示着...</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>〜とあんじしている</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>〜とする</t>
+          <t>受け持つ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>视为...，当作...</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>负责，担任</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>うけもつ</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>〜にしたがって</t>
+          <t>だって</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>随着...；遵照...</t>
+          <t>因为；即便是</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -682,16 +690,16 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>〜がないか</t>
+          <t>〜にびっくりする</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>是否…</t>
+          <t>对...感到惊讶</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -703,75 +711,63 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>求める</t>
+          <t>〜がないか</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>购买,寻求，要求</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>もとめる</t>
-        </is>
-      </c>
+          <t>是否…</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>〜の場合</t>
+          <t>〜にもとづいて</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>...的情况下</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>〜のばあい</t>
-        </is>
-      </c>
+          <t>根据...，基于...</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>改めて</t>
+          <t>〜にしたがって</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>重新，再次</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>あらためて</t>
-        </is>
-      </c>
+          <t>随着...；遵照...</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>だって</t>
+          <t>いざ〜となると</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>因为；即便是</t>
+          <t>一旦到了...的时候</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -779,37 +775,33 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>受け持つ</t>
+          <t>かえって</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>负责，担任</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>うけもつ</t>
-        </is>
-      </c>
+          <t>反而，反倒</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ようです</t>
+          <t>こいつら</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>好像...，似乎...</t>
+          <t>这些家伙们（粗鲁说法）</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -817,40 +809,40 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>〜と暗示している</t>
+          <t>あたりまえに</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>暗示着...</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>〜とあんじしている</t>
-        </is>
-      </c>
+          <t>理所当然地</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>あらためて</t>
+          <t>取り入れる</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>重新，再次</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>引进，采纳</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>とりいれる</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -859,19 +851,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>〜方がいる</t>
+          <t>～っていうのは</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>有...的人（敬语）</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>〜かたがいる</t>
-        </is>
-      </c>
+          <t>所谓…</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -880,12 +868,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ぽつんと</t>
+          <t>まるで〜ように</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>孤零零地</t>
+          <t>简直就像...一样</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -893,33 +881,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>〜にびっくりする</t>
+          <t>ずいぶん</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>对...感到惊讶</t>
+          <t>相当，非常</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ぷつんと-&gt;急匆匆地</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>わずか</t>
+          <t>あろう</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>仅仅，一点点</t>
+          <t>同“だろう”</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -927,19 +919,23 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>いずれも</t>
+          <t>〜の場合</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>任意的</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>...的情况下</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>〜のばあい</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -948,16 +944,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>つい</t>
+          <t>いままで</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>不由得，不知不觉地</t>
+          <t>到现在为止</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>これまで-&gt;过往，以前</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -965,12 +965,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>しっかり</t>
+          <t>なりきる</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>踏实地,好好地，牢固地</t>
+          <t>完全变成，扮演得惟妙惟肖</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -978,16 +978,16 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>はずかしい</t>
+          <t>ようです</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>害羞的，不好意思的</t>
+          <t>好像...，似乎...</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -995,16 +995,16 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>〜にしろ〜にしろ</t>
+          <t>〜とする</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>无论是...还是...</t>
+          <t>视为...，当作...</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1012,21 +1012,21 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>助手席</t>
+          <t>改めて</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>副驾驶座</t>
+          <t>重新，再次</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>じょしゅせき</t>
+          <t>あらためて</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1037,20 +1037,16 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ずいぶん</t>
+          <t>まとめ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>相当，非常</t>
+          <t>总结，归纳</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>ぷつんと-&gt;急匆匆地</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1058,20 +1054,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>〜となっている</t>
+          <t>すでに</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>(规定、状态)是...</t>
+          <t>已经</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>～ことになります-&gt;规定…</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1079,15 +1071,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>これまで</t>
+          <t>される方</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>至今为止</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>被动表尊他</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>されるかた</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -1096,29 +1092,33 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>なお</t>
+          <t>迷惑になります</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>另外，再者</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>会给人添麻烦</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>めいわくになります</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>まるで〜ように</t>
+          <t>あらゆる</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>简直就像...一样</t>
+          <t>所有的，一切的</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1126,16 +1126,16 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>～っていうのは</t>
+          <t>～ように</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>所谓…</t>
+          <t>正如…;为了…</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>どうせ</t>
+          <t>〜のは〜ためだ・からだ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>反正，总归</t>
+          <t>(之所以)...是因为...</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1164,36 +1164,36 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>用件</t>
+          <t>サークル</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>事情，要事</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>ようけん</t>
-        </is>
-      </c>
+          <t>社团，圈子</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>まとめ</t>
+          <t>働き</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>总结，归纳</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>工作；作用</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>はたらき</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>～によって</t>
+          <t>〜を〜する</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>通过…</t>
+          <t>担任(职务)，使(状态)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1219,19 +1219,15 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>作り声</t>
+          <t>もともと</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>假声</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>つくりごえ</t>
-        </is>
-      </c>
+          <t>原本，本来</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -1240,49 +1236,61 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>〜につながる</t>
+          <t>お願いがあります</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>与...相连，导致...</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>有事相求</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>おねがいがあります</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>そのため</t>
+          <t>持参</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>因此，所以</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>带来，自备</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>じさん</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>〜できませんでしょうか</t>
+          <t>〜に通う</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>能否...呢？（礼貌请求）</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>定期去（某地）</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>〜にかよう</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -1291,15 +1299,19 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>におい</t>
+          <t>受験する</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>味道，气味</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>参加考试</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>じゅけんする</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -1308,17 +1320,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>〜に通う</t>
+          <t>助手席</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>定期去（某地）</t>
+          <t>副驾驶座</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>〜にかよう</t>
+          <t>じょしゅせき</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -1329,19 +1341,15 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>受験する</t>
+          <t>におい</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>参加考试</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>じゅけんする</t>
-        </is>
-      </c>
+          <t>味道，气味</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
@@ -1350,19 +1358,15 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>迷惑になります</t>
+          <t>〜できませんでしょうか</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>会给人添麻烦</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>めいわくになります</t>
-        </is>
-      </c>
+          <t>能否...呢？（礼貌请求）</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
@@ -1371,33 +1375,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>される方</t>
+          <t>そのため</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>被动表尊他</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>されるかた</t>
-        </is>
-      </c>
+          <t>因此，所以</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>あらゆる</t>
+          <t>〜につながる</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>所有的，一切的</t>
+          <t>与...相连，导致...</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -1409,15 +1409,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>～ように</t>
+          <t>作り声</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>正如…;为了…</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>假声</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>つくりごえ</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -1426,12 +1430,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>〜のは〜ためだ・からだ</t>
+          <t>～によって</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>(之所以)...是因为...</t>
+          <t>通过…</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -1443,36 +1447,36 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>すでに</t>
+          <t>用件</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>已经</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>事情，要事</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ようけん</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>働き</t>
+          <t>どうせ</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>工作；作用</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>はたらき</t>
-        </is>
-      </c>
+          <t>反正，总归</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -1481,12 +1485,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>〜を〜する</t>
+          <t>なお</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>担任(职务)，使(状态)</t>
+          <t>另外，再者</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -1498,12 +1502,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>もともと</t>
+          <t>これまで</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>原本，本来</t>
+          <t>至今为止</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -1511,24 +1515,24 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>お願いがあります</t>
+          <t>〜となっている</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>有事相求</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>おねがいがあります</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>(规定、状态)是...</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>～ことになります-&gt;规定…</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1536,12 +1540,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>サークル</t>
+          <t>〜にしろ〜にしろ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>社团，圈子</t>
+          <t>无论是...还是...</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -1553,19 +1557,15 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>持参</t>
+          <t>はずかしい</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>带来，自备</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>じさん</t>
-        </is>
-      </c>
+          <t>害羞的，不好意思的</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">

--- a/READING/4_21_12.xlsx
+++ b/READING/4_21_12.xlsx
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -487,21 +487,21 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>求める</t>
+          <t>受け持つ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>购买,寻求，要求</t>
+          <t>负责，担任</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>もとめる</t>
+          <t>うけもつ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -512,29 +512,33 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>しっかり</t>
+          <t>取り入れる</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>踏实地,好好地，牢固地</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>引进，采纳</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>とりいれる</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>つい</t>
+          <t>〜にしたがって</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>不由得，不知不觉地</t>
+          <t>随着...；遵照...</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -542,16 +546,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>いずれも</t>
+          <t>あたりまえに</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>任意的</t>
+          <t>理所当然地</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -559,16 +563,16 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>わずか</t>
+          <t>いずれも</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>仅仅，一点点</t>
+          <t>任意的</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -576,7 +580,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -593,23 +597,19 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>〜方がいる</t>
+          <t>しっかり</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>有...的人（敬语）</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>〜かたがいる</t>
-        </is>
-      </c>
+          <t>踏实地,好好地，牢固地</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -618,36 +618,36 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>あらためて</t>
+          <t>〜と暗示している</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>重新，再次</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>暗示着...</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>〜とあんじしている</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>〜と暗示している</t>
+          <t>あらためて</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>暗示着...</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>〜とあんじしている</t>
-        </is>
-      </c>
+          <t>重新，再次</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -656,33 +656,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>受け持つ</t>
+          <t>だって</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>负责，担任</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>うけもつ</t>
-        </is>
-      </c>
+          <t>因为；即便是</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>だって</t>
+          <t>〜にもとづいて</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>因为；即便是</t>
+          <t>根据...，基于...</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -690,16 +686,16 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>〜にびっくりする</t>
+          <t>いざ〜となると</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>对...感到惊讶</t>
+          <t>一旦到了...的时候</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -707,16 +703,16 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>〜がないか</t>
+          <t>かえって</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>是否…</t>
+          <t>反而，反倒</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -724,16 +720,16 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>〜にもとづいて</t>
+          <t>こいつら</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>根据...，基于...</t>
+          <t>这些家伙们（粗鲁说法）</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -741,16 +737,16 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>〜にしたがって</t>
+          <t>〜にびっくりする</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>随着...；遵照...</t>
+          <t>对...感到惊讶</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -758,16 +754,16 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>いざ〜となると</t>
+          <t>つい</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>一旦到了...的时候</t>
+          <t>不由得，不知不觉地</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -779,29 +775,33 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>かえって</t>
+          <t>求める</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>反而，反倒</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>购买,寻求，要求</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>もとめる</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>こいつら</t>
+          <t>〜がないか</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>这些家伙们（粗鲁说法）</t>
+          <t>是否…</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -809,19 +809,23 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>あたりまえに</t>
+          <t>〜方がいる</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>理所当然地</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>有...的人（敬语）</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>〜かたがいる</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -830,24 +834,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>取り入れる</t>
+          <t>わずか</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>引进，采纳</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>とりいれる</t>
-        </is>
-      </c>
+          <t>仅仅，一点点</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -881,37 +881,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ずいぶん</t>
+          <t>いままで</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>相当，非常</t>
+          <t>到现在为止</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ぷつんと-&gt;急匆匆地</t>
+          <t>これまで-&gt;过往，以前</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>あろう</t>
+          <t>なりきる</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>同“だろう”</t>
+          <t>完全变成，扮演得惟妙惟肖</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -919,61 +919,61 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>〜の場合</t>
+          <t>〜とする</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>...的情况下</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>〜のばあい</t>
-        </is>
-      </c>
+          <t>视为...，当作...</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>いままで</t>
+          <t>ずいぶん</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>到现在为止</t>
+          <t>相当，非常</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>これまで-&gt;过往，以前</t>
+          <t>ぷつんと-&gt;急匆匆地</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>なりきる</t>
+          <t>〜の場合</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>完全变成，扮演得惟妙惟肖</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>...的情况下</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>〜のばあい</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -995,16 +995,16 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>〜とする</t>
+          <t>まとめ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>视为...，当作...</t>
+          <t>总结，归纳</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1016,19 +1016,15 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>改めて</t>
+          <t>あろう</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>重新，再次</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>あらためて</t>
-        </is>
-      </c>
+          <t>同“だろう”</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1037,108 +1033,116 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>まとめ</t>
+          <t>〜に通う</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>总结，归纳</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>定期去（某地）</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>〜にかよう</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>すでに</t>
+          <t>改めて</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>已经</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>重新，再次</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>あらためて</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>される方</t>
+          <t>〜につながる</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>被动表尊他</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>されるかた</t>
-        </is>
-      </c>
+          <t>与...相连，导致...</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>迷惑になります</t>
+          <t>どうせ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>会给人添麻烦</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>めいわくになります</t>
-        </is>
-      </c>
+          <t>反正，总归</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>あらゆる</t>
+          <t>〜となっている</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>所有的，一切的</t>
+          <t>(规定、状态)是...</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>～ことになります-&gt;规定…</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>～ように</t>
+          <t>持参</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>正如…;为了…</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>带来，自备</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>じさん</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -1147,15 +1151,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>〜のは〜ためだ・からだ</t>
+          <t>される方</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>(之所以)...是因为...</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>被动表尊他</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>されるかた</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
@@ -1164,15 +1172,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>サークル</t>
+          <t>迷惑になります</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>社团，圈子</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>会给人添麻烦</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>めいわくになります</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
@@ -1181,19 +1193,15 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>働き</t>
+          <t>あらゆる</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>工作；作用</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>はたらき</t>
-        </is>
-      </c>
+          <t>所有的，一切的</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -1202,12 +1210,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>〜を〜する</t>
+          <t>～ように</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>担任(职务)，使(状态)</t>
+          <t>正如…;为了…</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1219,12 +1227,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>もともと</t>
+          <t>〜のは〜ためだ・からだ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>原本，本来</t>
+          <t>(之所以)...是因为...</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1236,61 +1244,53 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>お願いがあります</t>
+          <t>サークル</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>有事相求</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>おねがいがあります</t>
-        </is>
-      </c>
+          <t>社团，圈子</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>持参</t>
+          <t>働き</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>带来，自备</t>
+          <t>工作；作用</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>じさん</t>
+          <t>はたらき</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>〜に通う</t>
+          <t>〜を〜する</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>定期去（某地）</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>〜にかよう</t>
-        </is>
-      </c>
+          <t>担任(职务)，使(状态)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -1299,19 +1299,15 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>受験する</t>
+          <t>もともと</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>参加考试</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>じゅけんする</t>
-        </is>
-      </c>
+          <t>原本，本来</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -1320,17 +1316,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>助手席</t>
+          <t>お願いがあります</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>副驾驶座</t>
+          <t>有事相求</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>じょしゅせき</t>
+          <t>おねがいがあります</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -1341,15 +1337,19 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>におい</t>
+          <t>受験する</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>味道，气味</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>参加考试</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>じゅけんする</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>〜できませんでしょうか</t>
+          <t>そのため</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>能否...呢？（礼貌请求）</t>
+          <t>因此，所以</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>そのため</t>
+          <t>におい</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>因此，所以</t>
+          <t>味道，气味</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -1388,19 +1388,23 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>〜につながる</t>
+          <t>助手席</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>与...相连，导致...</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>副驾驶座</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>じょしゅせき</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -1464,16 +1468,16 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>どうせ</t>
+          <t>なお</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>反正，总归</t>
+          <t>另外，再者</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -1485,12 +1489,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>なお</t>
+          <t>これまで</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>另外，再者</t>
+          <t>至今为止</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -1502,12 +1506,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>これまで</t>
+          <t>〜にしろ〜にしろ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>至今为止</t>
+          <t>无论是...还是...</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -1515,24 +1519,20 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>〜となっている</t>
+          <t>はずかしい</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>(规定、状态)是...</t>
+          <t>害羞的，不好意思的</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>～ことになります-&gt;规定…</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>〜にしろ〜にしろ</t>
+          <t>〜できませんでしょうか</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>无论是...还是...</t>
+          <t>能否...呢？（礼貌请求）</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>はずかしい</t>
+          <t>すでに</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>害羞的，不好意思的</t>
+          <t>已经</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>

--- a/READING/4_21_12.xlsx
+++ b/READING/4_21_12.xlsx
@@ -466,82 +466,74 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>〜による</t>
+          <t>あたりまえに</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>根据...；由于...</t>
+          <t>理所当然地</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>～によると-&gt;根据…，按照…</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>受け持つ</t>
+          <t>あらためて</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>负责，担任</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>うけもつ</t>
-        </is>
-      </c>
+          <t>重新，再次</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>取り入れる</t>
+          <t>ぽつんと</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>引进，采纳</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>とりいれる</t>
-        </is>
-      </c>
+          <t>孤零零地</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>〜にしたがって</t>
+          <t>受け持つ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>随着...；遵照...</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>负责，担任</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>うけもつ</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -550,16 +542,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>あたりまえに</t>
+          <t>〜による</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>理所当然地</t>
+          <t>根据...；由于...</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>～によると-&gt;根据…，按照…</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -567,12 +563,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>いずれも</t>
+          <t>だって</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>任意的</t>
+          <t>因为；即便是</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -580,16 +576,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ぽつんと</t>
+          <t>わずか</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>孤零零地</t>
+          <t>仅仅，一点点</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -597,16 +593,16 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>しっかり</t>
+          <t>まるで〜ように</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>踏实地,好好地，牢固地</t>
+          <t>简直就像...一样</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -614,23 +610,19 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>〜と暗示している</t>
+          <t>いずれも</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>暗示着...</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>〜とあんじしている</t>
-        </is>
-      </c>
+          <t>任意的</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -639,12 +631,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>あらためて</t>
+          <t>〜にびっくりする</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>重新，再次</t>
+          <t>对...感到惊讶</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -652,16 +644,16 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>だって</t>
+          <t>〜にもとづいて</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>因为；即便是</t>
+          <t>根据...，基于...</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -673,12 +665,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>〜にもとづいて</t>
+          <t>いざ〜となると</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>根据...，基于...</t>
+          <t>一旦到了...的时候</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -690,12 +682,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>いざ〜となると</t>
+          <t>こいつら</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>一旦到了...的时候</t>
+          <t>这些家伙们（粗鲁说法）</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -703,16 +695,16 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>かえって</t>
+          <t>〜にしたがって</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>反而，反倒</t>
+          <t>随着...；遵照...</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -720,16 +712,16 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>こいつら</t>
+          <t>かえって</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>这些家伙们（粗鲁说法）</t>
+          <t>反而，反倒</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -737,16 +729,16 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>〜にびっくりする</t>
+          <t>なりきる</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>对...感到惊讶</t>
+          <t>完全变成，扮演得惟妙惟肖</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -754,7 +746,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -775,55 +767,55 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>求める</t>
+          <t>しっかり</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>购买,寻求，要求</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>もとめる</t>
-        </is>
-      </c>
+          <t>踏实地,好好地，牢固地</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>〜がないか</t>
+          <t>取り入れる</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>是否…</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>引进，采纳</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>とりいれる</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>〜方がいる</t>
+          <t>〜と暗示している</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>有...的人（敬语）</t>
+          <t>暗示着...</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>〜かたがいる</t>
+          <t>〜とあんじしている</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -834,12 +826,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>わずか</t>
+          <t>～っていうのは</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>仅仅，一点点</t>
+          <t>所谓…</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -851,12 +843,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>～っていうのは</t>
+          <t>〜とする</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>所谓…</t>
+          <t>视为...，当作...</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -868,15 +860,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>まるで〜ように</t>
+          <t>求める</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>简直就像...一样</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>购买,寻求，要求</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>もとめる</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -885,20 +881,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>いままで</t>
+          <t>〜がないか</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>到现在为止</t>
+          <t>是否…</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>これまで-&gt;过往，以前</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -906,72 +898,80 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>なりきる</t>
+          <t>改めて</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>完全变成，扮演得惟妙惟肖</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>重新，再次</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>あらためて</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>〜とする</t>
+          <t>いままで</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>视为...，当作...</t>
+          <t>到现在为止</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>これまで-&gt;过往，以前</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ずいぶん</t>
+          <t>持参</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>相当，非常</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>ぷつんと-&gt;急匆匆地</t>
-        </is>
-      </c>
+          <t>带来，自备</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>じさん</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>〜の場合</t>
+          <t>〜方がいる</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>...的情况下</t>
+          <t>有...的人（敬语）</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>〜のばあい</t>
+          <t>〜かたがいる</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1016,16 +1016,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>あろう</t>
+          <t>ずいぶん</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>同“だろう”</t>
+          <t>相当，非常</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ぷつんと-&gt;急匆匆地</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1033,40 +1037,36 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>〜に通う</t>
+          <t>〜の場合</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>定期去（某地）</t>
+          <t>...的情况下</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>〜にかよう</t>
+          <t>〜のばあい</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>改めて</t>
+          <t>〜につながる</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>重新，再次</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>あらためて</t>
-        </is>
-      </c>
+          <t>与...相连，导致...</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -1075,15 +1075,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>〜につながる</t>
+          <t>〜に通う</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>与...相连，导致...</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>定期去（某地）</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>〜にかよう</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -1126,23 +1130,19 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>持参</t>
+          <t>あろう</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>带来，自备</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>じさん</t>
-        </is>
-      </c>
+          <t>同“だろう”</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -1151,19 +1151,15 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>される方</t>
+          <t>そのため</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>被动表尊他</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>されるかた</t>
-        </is>
-      </c>
+          <t>因此，所以</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
@@ -1172,17 +1168,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>迷惑になります</t>
+          <t>される方</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>会给人添麻烦</t>
+          <t>被动表尊他</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>めいわくになります</t>
+          <t>されるかた</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1193,15 +1189,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>あらゆる</t>
+          <t>迷惑になります</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>所有的，一切的</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>会给人添麻烦</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>めいわくになります</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>～ように</t>
+          <t>あらゆる</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>正如…;为了…</t>
+          <t>所有的，一切的</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>〜のは〜ためだ・からだ</t>
+          <t>～ように</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>(之所以)...是因为...</t>
+          <t>正如…;为了…</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>サークル</t>
+          <t>〜のは〜ためだ・からだ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>社团，圈子</t>
+          <t>(之所以)...是因为...</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1261,19 +1261,15 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>働き</t>
+          <t>サークル</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>工作；作用</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>はたらき</t>
-        </is>
-      </c>
+          <t>社团，圈子</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -1282,15 +1278,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>〜を〜する</t>
+          <t>働き</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>担任(职务)，使(状态)</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>工作；作用</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>はたらき</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>もともと</t>
+          <t>〜を〜する</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>原本，本来</t>
+          <t>担任(职务)，使(状态)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1316,19 +1316,15 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>お願いがあります</t>
+          <t>もともと</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>有事相求</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>おねがいがあります</t>
-        </is>
-      </c>
+          <t>原本，本来</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -1358,15 +1354,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>そのため</t>
+          <t>助手席</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>因此，所以</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>副驾驶座</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>じょしゅせき</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
@@ -1375,15 +1375,19 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>におい</t>
+          <t>お願いがあります</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>味道，气味</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>有事相求</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>おねがいがあります</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -1392,17 +1396,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>助手席</t>
+          <t>作り声</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>副驾驶座</t>
+          <t>假声</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>じょしゅせき</t>
+          <t>つくりごえ</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -1413,19 +1417,15 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>作り声</t>
+          <t>～によって</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>假声</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>つくりごえ</t>
-        </is>
-      </c>
+          <t>通过…</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -1434,15 +1434,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>～によって</t>
+          <t>用件</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>通过…</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>事情，要事</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ようけん</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -1451,19 +1455,15 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>用件</t>
+          <t>なお</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>事情，要事</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>ようけん</t>
-        </is>
-      </c>
+          <t>另外，再者</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>なお</t>
+          <t>これまで</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>另外，再者</t>
+          <t>至今为止</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>これまで</t>
+          <t>〜にしろ〜にしろ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>至今为止</t>
+          <t>无论是...还是...</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>〜にしろ〜にしろ</t>
+          <t>はずかしい</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>无论是...还是...</t>
+          <t>害羞的，不好意思的</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>はずかしい</t>
+          <t>〜できませんでしょうか</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>害羞的，不好意思的</t>
+          <t>能否...呢？（礼貌请求）</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -1540,12 +1540,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>〜できませんでしょうか</t>
+          <t>すでに</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>能否...呢？（礼貌请求）</t>
+          <t>已经</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>すでに</t>
+          <t>におい</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>已经</t>
+          <t>味道，气味</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>

--- a/READING/4_21_12.xlsx
+++ b/READING/4_21_12.xlsx
@@ -466,58 +466,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>〜による</t>
+          <t>あたりまえに</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>根据...；由于...</t>
+          <t>理所当然地</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>～によると-&gt;根据…，按照…</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>求める</t>
+          <t>あらためて</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>购买,寻求，要求</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>もとめる</t>
-        </is>
-      </c>
+          <t>重新，再次</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>しっかり</t>
+          <t>ぽつんと</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>踏实地,好好地，牢固地</t>
+          <t>孤零零地</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -525,50 +517,58 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>つい</t>
+          <t>受け持つ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>不由得，不知不觉地</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>负责，担任</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>うけもつ</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>いずれも</t>
+          <t>〜による</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>任意的</t>
+          <t>根据...；由于...</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>～によると-&gt;根据…，按照…</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>わずか</t>
+          <t>だって</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>仅仅，一点点</t>
+          <t>因为；即便是</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -576,16 +576,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ぽつんと</t>
+          <t>わずか</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>孤零零地</t>
+          <t>仅仅，一点点</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -593,37 +593,33 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>〜方がいる</t>
+          <t>まるで〜ように</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>有...的人（敬语）</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>〜かたがいる</t>
-        </is>
-      </c>
+          <t>简直就像...一样</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>あらためて</t>
+          <t>いずれも</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>重新，再次</t>
+          <t>任意的</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -631,58 +627,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>〜と暗示している</t>
+          <t>〜にびっくりする</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>暗示着...</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>〜とあんじしている</t>
-        </is>
-      </c>
+          <t>对...感到惊讶</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>受け持つ</t>
+          <t>〜にもとづいて</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>负责，担任</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>うけもつ</t>
-        </is>
-      </c>
+          <t>根据...，基于...</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>だって</t>
+          <t>いざ〜となると</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>因为；即便是</t>
+          <t>一旦到了...的时候</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -690,16 +678,16 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>〜にびっくりする</t>
+          <t>こいつら</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>对...感到惊讶</t>
+          <t>这些家伙们（粗鲁说法）</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -707,16 +695,16 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>〜がないか</t>
+          <t>〜にしたがって</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>是否…</t>
+          <t>随着...；遵照...</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -728,12 +716,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>〜にもとづいて</t>
+          <t>かえって</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>根据...，基于...</t>
+          <t>反而，反倒</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -745,12 +733,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>〜にしたがって</t>
+          <t>なりきる</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>随着...；遵照...</t>
+          <t>完全变成，扮演得惟妙惟肖</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -758,16 +746,16 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>いざ〜となると</t>
+          <t>つい</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>一旦到了...的时候</t>
+          <t>不由得，不知不觉地</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -779,12 +767,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>かえって</t>
+          <t>しっかり</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>反而，反倒</t>
+          <t>踏实地,好好地，牢固地</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -796,15 +784,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>こいつら</t>
+          <t>取り入れる</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>这些家伙们（粗鲁说法）</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>引进，采纳</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>とりいれる</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -813,15 +805,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>あたりまえに</t>
+          <t>〜と暗示している</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>理所当然地</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>暗示着...</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>〜とあんじしている</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -830,33 +826,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>取り入れる</t>
+          <t>～っていうのは</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>引进，采纳</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>とりいれる</t>
-        </is>
-      </c>
+          <t>所谓…</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>～っていうのは</t>
+          <t>〜とする</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>所谓…</t>
+          <t>视为...，当作...</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -864,79 +856,83 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>まるで〜ように</t>
+          <t>求める</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>简直就像...一样</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>购买,寻求，要求</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>もとめる</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ずいぶん</t>
+          <t>〜がないか</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>相当，非常</t>
+          <t>是否…</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>ぷつんと-&gt;急匆匆地</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>あろう</t>
+          <t>改めて</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>同“だろう”</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>重新，再次</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>あらためて</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>〜の場合</t>
+          <t>いままで</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>...的情况下</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>〜のばあい</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>到现在为止</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>これまで-&gt;过往，以前</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -944,20 +940,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>いままで</t>
+          <t>持参</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>到现在为止</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>これまで-&gt;过往，以前</t>
-        </is>
-      </c>
+          <t>带来，自备</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>じさん</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -965,15 +961,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>なりきる</t>
+          <t>〜方がいる</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>完全变成，扮演得惟妙惟肖</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>有...的人（敬语）</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>〜かたがいる</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -995,16 +995,16 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>〜とする</t>
+          <t>まとめ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>视为...，当作...</t>
+          <t>总结，归纳</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1016,20 +1016,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>改めて</t>
+          <t>ずいぶん</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>重新，再次</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>あらためて</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>相当，非常</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ぷつんと-&gt;急匆匆地</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1037,29 +1037,33 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>まとめ</t>
+          <t>〜の場合</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>总结，归纳</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>...的情况下</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>〜のばあい</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>すでに</t>
+          <t>〜につながる</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>已经</t>
+          <t>与...相连，导致...</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1067,75 +1071,75 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>される方</t>
+          <t>〜に通う</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>被动表尊他</t>
+          <t>定期去（某地）</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>されるかた</t>
+          <t>〜にかよう</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>迷惑になります</t>
+          <t>どうせ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>会给人添麻烦</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>めいわくになります</t>
-        </is>
-      </c>
+          <t>反正，总归</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>あらゆる</t>
+          <t>〜となっている</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>所有的，一切的</t>
+          <t>(规定、状态)是...</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>～ことになります-&gt;规定…</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>～ように</t>
+          <t>あろう</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>正如…;为了…</t>
+          <t>同“だろう”</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1147,12 +1151,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>〜のは〜ためだ・からだ</t>
+          <t>そのため</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>(之所以)...是因为...</t>
+          <t>因此，所以</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1164,15 +1168,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>サークル</t>
+          <t>される方</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>社团，圈子</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>被动表尊他</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>されるかた</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
@@ -1181,17 +1189,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>働き</t>
+          <t>迷惑になります</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>工作；作用</t>
+          <t>会给人添麻烦</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>はたらき</t>
+          <t>めいわくになります</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1202,12 +1210,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>〜を〜する</t>
+          <t>あらゆる</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>担任(职务)，使(状态)</t>
+          <t>所有的，一切的</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1219,12 +1227,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>もともと</t>
+          <t>～ように</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>原本，本来</t>
+          <t>正如…;为了…</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1236,59 +1244,51 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>お願いがあります</t>
+          <t>〜のは〜ためだ・からだ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>有事相求</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>おねがいがあります</t>
-        </is>
-      </c>
+          <t>(之所以)...是因为...</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>持参</t>
+          <t>サークル</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>带来，自备</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>じさん</t>
-        </is>
-      </c>
+          <t>社团，圈子</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>〜に通う</t>
+          <t>働き</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>定期去（某地）</t>
+          <t>工作；作用</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>〜にかよう</t>
+          <t>はたらき</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -1299,19 +1299,15 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>受験する</t>
+          <t>〜を〜する</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>参加考试</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>じゅけんする</t>
-        </is>
-      </c>
+          <t>担任(职务)，使(状态)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -1320,19 +1316,15 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>助手席</t>
+          <t>もともと</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>副驾驶座</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>じょしゅせき</t>
-        </is>
-      </c>
+          <t>原本，本来</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -1341,15 +1333,19 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>におい</t>
+          <t>受験する</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>味道，气味</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>参加考试</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>じゅけんする</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
@@ -1358,15 +1354,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>〜できませんでしょうか</t>
+          <t>助手席</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>能否...呢？（礼貌请求）</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>副驾驶座</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>じょしゅせき</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
@@ -1375,32 +1375,40 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>そのため</t>
+          <t>お願いがあります</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>因此，所以</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>有事相求</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>おねがいがあります</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>〜につながる</t>
+          <t>作り声</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>与...相连，导致...</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>假声</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>つくりごえ</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -1409,19 +1417,15 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>作り声</t>
+          <t>～によって</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>假声</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>つくりごえ</t>
-        </is>
-      </c>
+          <t>通过…</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -1430,15 +1434,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>～によって</t>
+          <t>用件</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>通过…</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>事情，要事</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ようけん</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -1447,33 +1455,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>用件</t>
+          <t>なお</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>事情，要事</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>ようけん</t>
-        </is>
-      </c>
+          <t>另外，再者</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>どうせ</t>
+          <t>これまで</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>反正，总归</t>
+          <t>至今为止</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -1485,12 +1489,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>なお</t>
+          <t>〜にしろ〜にしろ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>另外，再者</t>
+          <t>无论是...还是...</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -1502,12 +1506,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>これまで</t>
+          <t>はずかしい</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>至今为止</t>
+          <t>害羞的，不好意思的</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -1515,24 +1519,20 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>〜となっている</t>
+          <t>〜できませんでしょうか</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>(规定、状态)是...</t>
+          <t>能否...呢？（礼貌请求）</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>～ことになります-&gt;规定…</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>〜にしろ〜にしろ</t>
+          <t>すでに</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>无论是...还是...</t>
+          <t>已经</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>はずかしい</t>
+          <t>におい</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>害羞的，不好意思的</t>
+          <t>味道，气味</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>

--- a/READING/4_21_12.xlsx
+++ b/READING/4_21_12.xlsx
@@ -466,50 +466,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>あたりまえに</t>
+          <t>〜による</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>理所当然地</t>
+          <t>根据...；由于...</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>～によると-&gt;根据…，按照…</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>あらためて</t>
+          <t>求める</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>重新，再次</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>购买,寻求，要求</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>もとめる</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ぽつんと</t>
+          <t>しっかり</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>孤零零地</t>
+          <t>踏实地,好好地，牢固地</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -517,58 +525,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>受け持つ</t>
+          <t>つい</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>负责，担任</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>うけもつ</t>
-        </is>
-      </c>
+          <t>不由得，不知不觉地</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>〜による</t>
+          <t>いずれも</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>根据...；由于...</t>
+          <t>任意的</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>～によると-&gt;根据…，按照…</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>だって</t>
+          <t>わずか</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>因为；即便是</t>
+          <t>仅仅，一点点</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -576,16 +576,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>わずか</t>
+          <t>ぽつんと</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>仅仅，一点点</t>
+          <t>孤零零地</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -593,33 +593,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>まるで〜ように</t>
+          <t>〜方がいる</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>简直就像...一样</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>有...的人（敬语）</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>〜かたがいる</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>いずれも</t>
+          <t>あらためて</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>任意的</t>
+          <t>重新，再次</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -627,50 +631,58 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>〜にびっくりする</t>
+          <t>〜と暗示している</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>对...感到惊讶</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>暗示着...</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>〜とあんじしている</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>〜にもとづいて</t>
+          <t>受け持つ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>根据...，基于...</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>负责，担任</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>うけもつ</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>いざ〜となると</t>
+          <t>だって</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>一旦到了...的时候</t>
+          <t>因为；即便是</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -678,16 +690,16 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>こいつら</t>
+          <t>〜にびっくりする</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>这些家伙们（粗鲁说法）</t>
+          <t>对...感到惊讶</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -695,16 +707,16 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>〜にしたがって</t>
+          <t>〜がないか</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>随着...；遵照...</t>
+          <t>是否…</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -716,12 +728,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>かえって</t>
+          <t>〜にもとづいて</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>反而，反倒</t>
+          <t>根据...，基于...</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -733,12 +745,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>なりきる</t>
+          <t>〜にしたがって</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>完全变成，扮演得惟妙惟肖</t>
+          <t>随着...；遵照...</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -746,16 +758,16 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>つい</t>
+          <t>いざ〜となると</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>不由得，不知不觉地</t>
+          <t>一旦到了...的时候</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -767,12 +779,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>しっかり</t>
+          <t>かえって</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>踏实地,好好地，牢固地</t>
+          <t>反而，反倒</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -784,19 +796,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>取り入れる</t>
+          <t>こいつら</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>引进，采纳</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>とりいれる</t>
-        </is>
-      </c>
+          <t>这些家伙们（粗鲁说法）</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -805,19 +813,15 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>〜と暗示している</t>
+          <t>あたりまえに</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>暗示着...</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>〜とあんじしている</t>
-        </is>
-      </c>
+          <t>理所当然地</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -826,29 +830,33 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>～っていうのは</t>
+          <t>取り入れる</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>所谓…</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>引进，采纳</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>とりいれる</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>〜とする</t>
+          <t>～っていうのは</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>视为...，当作...</t>
+          <t>所谓…</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -856,83 +864,79 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>求める</t>
+          <t>まるで〜ように</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>购买,寻求，要求</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>もとめる</t>
-        </is>
-      </c>
+          <t>简直就像...一样</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>〜がないか</t>
+          <t>ずいぶん</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>是否…</t>
+          <t>相当，非常</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ぷつんと-&gt;急匆匆地</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>改めて</t>
+          <t>あろう</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>重新，再次</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>あらためて</t>
-        </is>
-      </c>
+          <t>同“だろう”</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>いままで</t>
+          <t>〜の場合</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>到现在为止</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>これまで-&gt;过往，以前</t>
-        </is>
-      </c>
+          <t>...的情况下</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>〜のばあい</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -940,20 +944,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>持参</t>
+          <t>いままで</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>带来，自备</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>じさん</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>到现在为止</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>これまで-&gt;过往，以前</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -961,19 +965,15 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>〜方がいる</t>
+          <t>なりきる</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>有...的人（敬语）</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>〜かたがいる</t>
-        </is>
-      </c>
+          <t>完全变成，扮演得惟妙惟肖</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -995,16 +995,16 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>まとめ</t>
+          <t>〜とする</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>总结，归纳</t>
+          <t>视为...，当作...</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1016,20 +1016,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ずいぶん</t>
+          <t>改めて</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>相当，非常</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>ぷつんと-&gt;急匆匆地</t>
-        </is>
-      </c>
+          <t>重新，再次</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>あらためて</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1037,33 +1037,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>〜の場合</t>
+          <t>まとめ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>...的情况下</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>〜のばあい</t>
-        </is>
-      </c>
+          <t>总结，归纳</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>〜につながる</t>
+          <t>すでに</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>与...相连，导致...</t>
+          <t>已经</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1071,75 +1067,75 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>〜に通う</t>
+          <t>される方</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>定期去（某地）</t>
+          <t>被动表尊他</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>〜にかよう</t>
+          <t>されるかた</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>どうせ</t>
+          <t>迷惑になります</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>反正，总归</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>会给人添麻烦</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>めいわくになります</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>〜となっている</t>
+          <t>あらゆる</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>(规定、状态)是...</t>
+          <t>所有的，一切的</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>～ことになります-&gt;规定…</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>あろう</t>
+          <t>～ように</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>同“だろう”</t>
+          <t>正如…;为了…</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1151,12 +1147,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>そのため</t>
+          <t>〜のは〜ためだ・からだ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>因此，所以</t>
+          <t>(之所以)...是因为...</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1168,19 +1164,15 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>される方</t>
+          <t>サークル</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>被动表尊他</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>されるかた</t>
-        </is>
-      </c>
+          <t>社团，圈子</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
@@ -1189,17 +1181,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>迷惑になります</t>
+          <t>働き</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>会给人添麻烦</t>
+          <t>工作；作用</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>めいわくになります</t>
+          <t>はたらき</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1210,12 +1202,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>あらゆる</t>
+          <t>〜を〜する</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>所有的，一切的</t>
+          <t>担任(职务)，使(状态)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1227,12 +1219,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>～ように</t>
+          <t>もともと</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>正如…;为了…</t>
+          <t>原本，本来</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1244,51 +1236,59 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>〜のは〜ためだ・からだ</t>
+          <t>お願いがあります</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>(之所以)...是因为...</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>有事相求</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>おねがいがあります</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>サークル</t>
+          <t>持参</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>社团，圈子</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>带来，自备</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>じさん</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>働き</t>
+          <t>〜に通う</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>工作；作用</t>
+          <t>定期去（某地）</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>はたらき</t>
+          <t>〜にかよう</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -1299,15 +1299,19 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>〜を〜する</t>
+          <t>受験する</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>担任(职务)，使(状态)</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>参加考试</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>じゅけんする</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -1316,15 +1320,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>もともと</t>
+          <t>助手席</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>原本，本来</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>副驾驶座</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>じょしゅせき</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -1333,19 +1341,15 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>受験する</t>
+          <t>におい</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>参加考试</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>じゅけんする</t>
-        </is>
-      </c>
+          <t>味道，气味</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
@@ -1354,19 +1358,15 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>助手席</t>
+          <t>〜できませんでしょうか</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>副驾驶座</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>じょしゅせき</t>
-        </is>
-      </c>
+          <t>能否...呢？（礼貌请求）</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
@@ -1375,40 +1375,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>お願いがあります</t>
+          <t>そのため</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>有事相求</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>おねがいがあります</t>
-        </is>
-      </c>
+          <t>因此，所以</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>作り声</t>
+          <t>〜につながる</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>假声</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>つくりごえ</t>
-        </is>
-      </c>
+          <t>与...相连，导致...</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -1417,15 +1409,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>～によって</t>
+          <t>作り声</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>通过…</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>假声</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>つくりごえ</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -1434,19 +1430,15 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>用件</t>
+          <t>～によって</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>事情，要事</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>ようけん</t>
-        </is>
-      </c>
+          <t>通过…</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -1455,29 +1447,33 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>なお</t>
+          <t>用件</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>另外，再者</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>事情，要事</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ようけん</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>これまで</t>
+          <t>どうせ</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>至今为止</t>
+          <t>反正，总归</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -1489,12 +1485,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>〜にしろ〜にしろ</t>
+          <t>なお</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>无论是...还是...</t>
+          <t>另外，再者</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -1506,12 +1502,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>はずかしい</t>
+          <t>これまで</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>害羞的，不好意思的</t>
+          <t>至今为止</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -1519,20 +1515,24 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>〜できませんでしょうか</t>
+          <t>〜となっている</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>能否...呢？（礼貌请求）</t>
+          <t>(规定、状态)是...</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>～ことになります-&gt;规定…</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>すでに</t>
+          <t>〜にしろ〜にしろ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>已经</t>
+          <t>无论是...还是...</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>におい</t>
+          <t>はずかしい</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>味道，气味</t>
+          <t>害羞的，不好意思的</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>

--- a/READING/4_21_12.xlsx
+++ b/READING/4_21_12.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.75" customWidth="1" min="1" max="1"/>
@@ -463,10 +463,15 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -480,10 +485,15 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -497,6 +507,11 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -514,10 +529,15 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -531,6 +551,11 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -552,6 +577,11 @@
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -569,6 +599,11 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -586,6 +621,11 @@
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -603,6 +643,11 @@
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -620,6 +665,11 @@
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -637,6 +687,11 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -654,6 +709,11 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -671,6 +731,11 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -688,6 +753,11 @@
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -705,6 +775,11 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -722,6 +797,11 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -739,10 +819,15 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -756,6 +841,11 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -773,6 +863,11 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -790,6 +885,11 @@
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -807,10 +907,15 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -824,6 +929,11 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -845,6 +955,11 @@
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -862,6 +977,11 @@
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -879,10 +999,15 @@
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -896,6 +1021,11 @@
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -913,6 +1043,11 @@
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -930,6 +1065,11 @@
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -951,6 +1091,11 @@
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -968,6 +1113,11 @@
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -989,6 +1139,11 @@
           <t>～によると-&gt;根据…，按照…</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1010,6 +1165,11 @@
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1031,6 +1191,11 @@
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1052,6 +1217,11 @@
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1069,10 +1239,15 @@
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1086,6 +1261,11 @@
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1103,6 +1283,11 @@
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1120,6 +1305,11 @@
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1141,6 +1331,11 @@
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1158,6 +1353,11 @@
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1179,6 +1379,11 @@
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1196,6 +1401,11 @@
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1213,6 +1423,11 @@
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1230,6 +1445,11 @@
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1251,6 +1471,11 @@
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1268,6 +1493,11 @@
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1289,6 +1519,11 @@
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1306,6 +1541,11 @@
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1323,6 +1563,11 @@
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1344,6 +1589,11 @@
           <t>これまで-&gt;过往，以前</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1365,6 +1615,11 @@
           <t>いずれも-&gt;任意的</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1386,6 +1641,11 @@
           <t>～ことになります-&gt;规定…</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1403,6 +1663,11 @@
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1424,6 +1689,11 @@
           <t>ぷつんと-&gt;急匆匆地</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1441,6 +1711,11 @@
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1462,10 +1737,15 @@
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -1483,6 +1763,11 @@
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1500,6 +1785,11 @@
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1517,6 +1807,11 @@
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1538,6 +1833,11 @@
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1559,6 +1859,11 @@
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1576,6 +1881,11 @@
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1597,6 +1907,11 @@
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1618,6 +1933,11 @@
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1639,6 +1959,11 @@
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1656,6 +1981,11 @@
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1673,6 +2003,11 @@
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1694,6 +2029,11 @@
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1711,6 +2051,11 @@
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1732,6 +2077,11 @@
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1753,6 +2103,11 @@
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1774,6 +2129,11 @@
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1791,6 +2151,11 @@
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1808,6 +2173,11 @@
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1825,6 +2195,11 @@
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1842,6 +2217,11 @@
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1859,6 +2239,11 @@
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1876,6 +2261,11 @@
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -1893,6 +2283,11 @@
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -1910,6 +2305,11 @@
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -1927,6 +2327,11 @@
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -1948,6 +2353,11 @@
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -1965,6 +2375,11 @@
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -1982,6 +2397,11 @@
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
